--- a/data/estadisticas_poblacion_2026-09-25.xlsx
+++ b/data/estadisticas_poblacion_2026-09-25.xlsx
@@ -456,7 +456,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-25 17:47 UTC</t>
+          <t>2026-09-25 18:09 UTC</t>
         </is>
       </c>
     </row>
